--- a/exports/sales_call_report.xlsx
+++ b/exports/sales_call_report.xlsx
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -191,6 +191,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -531,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -696,8 +699,13 @@
         <v>33</v>
       </c>
     </row>
+    <row r="3" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G3" s="2"/>
+      <c r="I3" s="5"/>
+      <c r="W3" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/exports/sales_call_report.xlsx
+++ b/exports/sales_call_report.xlsx
@@ -180,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -195,6 +195,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -704,6 +705,21 @@
       <c r="I3" s="5"/>
       <c r="W3" s="4"/>
     </row>
+    <row r="4" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G4" s="6"/>
+      <c r="I4" s="3"/>
+      <c r="W4" s="4"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G5" s="2"/>
+      <c r="I5" s="5"/>
+      <c r="W5" s="4"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G6" s="2"/>
+      <c r="I6" s="5"/>
+      <c r="W6" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/exports/sales_call_report.xlsx
+++ b/exports/sales_call_report.xlsx
@@ -136,7 +136,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,6 +156,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -196,6 +201,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -720,6 +726,11 @@
       <c r="I6" s="5"/>
       <c r="W6" s="4"/>
     </row>
+    <row r="7" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G7" s="7"/>
+      <c r="I7" s="5"/>
+      <c r="W7" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/exports/sales_call_report.xlsx
+++ b/exports/sales_call_report.xlsx
@@ -136,7 +136,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -156,6 +156,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -196,6 +201,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -720,6 +729,46 @@
       <c r="I6" s="5"/>
       <c r="W6" s="4"/>
     </row>
+    <row r="7" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G7" s="7"/>
+      <c r="I7" s="8"/>
+      <c r="W7" s="4"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G8" s="2"/>
+      <c r="I8" s="5"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G9" s="2"/>
+      <c r="I9" s="3"/>
+      <c r="W9" s="4"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G10" s="2"/>
+      <c r="I10" s="3"/>
+      <c r="W10" s="4"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="W11" s="4"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G12" s="2"/>
+      <c r="I12" s="3"/>
+      <c r="W12" s="4"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G13" s="2"/>
+      <c r="I13" s="3"/>
+      <c r="W13" s="4"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G14" s="2"/>
+      <c r="I14" s="5"/>
+      <c r="W14" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/exports/sales_call_report.xlsx
+++ b/exports/sales_call_report.xlsx
@@ -185,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -202,6 +202,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -541,7 +544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -731,6 +734,16 @@
       <c r="I7" s="5"/>
       <c r="W7" s="4"/>
     </row>
+    <row r="8" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G8" s="2"/>
+      <c r="I8" s="5"/>
+      <c r="W8" s="4"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="7:23" x14ac:dyDescent="0.25">
+      <c r="G9" s="7"/>
+      <c r="I9" s="8"/>
+      <c r="W9" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
